--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.65688690531645</v>
+        <v>8.394244122113925</v>
       </c>
       <c r="D2" t="n">
-        <v>50.81780787263357</v>
+        <v>8.257893779302956</v>
       </c>
       <c r="E2" t="n">
-        <v>3.653472199216154</v>
+        <v>0.5936892323726252</v>
       </c>
       <c r="F2" t="n">
-        <v>3.102404007674381</v>
+        <v>0.504140651247087</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.77830261315252</v>
+        <v>7.276474174637285</v>
       </c>
       <c r="D3" t="n">
-        <v>45.60840620567313</v>
+        <v>7.411366008421885</v>
       </c>
       <c r="E3" t="n">
-        <v>3.653472199216154</v>
+        <v>0.5936892323726252</v>
       </c>
       <c r="F3" t="n">
-        <v>3.102404007674381</v>
+        <v>0.504140651247087</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.61870228001923</v>
+        <v>6.763039120503125</v>
       </c>
       <c r="D4" t="n">
-        <v>42.22165709450744</v>
+        <v>6.861019277857459</v>
       </c>
       <c r="E4" t="n">
-        <v>3.653472199216154</v>
+        <v>0.5936892323726252</v>
       </c>
       <c r="F4" t="n">
-        <v>3.102404007674381</v>
+        <v>0.504140651247087</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.04930790530128</v>
+        <v>7.320512534611459</v>
       </c>
       <c r="D5" t="n">
-        <v>45.06179857589733</v>
+        <v>7.322542268583317</v>
       </c>
       <c r="E5" t="n">
-        <v>3.653472199216154</v>
+        <v>0.5936892323726252</v>
       </c>
       <c r="F5" t="n">
-        <v>3.102404007674381</v>
+        <v>0.504140651247087</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
